--- a/node/suivi_site.xlsx
+++ b/node/suivi_site.xlsx
@@ -428,12 +428,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
@@ -442,7 +442,8 @@
     <col width="17" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="34" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -503,6 +504,11 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
+          <t>Mail Received Time</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
           <t>Duration</t>
         </is>
       </c>
@@ -563,7 +569,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>25:49:30</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>26:05:51</t>
         </is>
       </c>
     </row>
@@ -623,7 +634,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>09:07:43</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>09:24:04</t>
         </is>
       </c>
     </row>
@@ -683,7 +699,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>09:07:43</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>09:24:04</t>
         </is>
       </c>
     </row>
@@ -743,7 +764,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>09:07:43</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>09:24:04</t>
         </is>
       </c>
     </row>
@@ -803,7 +829,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>09:07:00</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>09:23:21</t>
         </is>
       </c>
     </row>
@@ -863,7 +894,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>08:05:09</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>08:21:30</t>
         </is>
       </c>
     </row>
@@ -923,7 +959,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>03:32:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>03:48:35</t>
         </is>
       </c>
     </row>
@@ -983,7 +1024,12 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>03:31:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>03:47:35</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1089,12 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>03:30:56</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>03:47:17</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1154,12 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>02:40:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>02:56:35</t>
         </is>
       </c>
     </row>
@@ -1163,34 +1219,39 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>02:40:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>02:56:35</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AC785</t>
+          <t>AC758</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GROBONOU_DAN</t>
+          <t>KOUASSI_DATEKRO</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AC785</t>
+          <t>AC758</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>YOBSC02</t>
+          <t>AGBSC22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABENGOUROU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1200,11 +1261,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56:47</t>
+          <t>2026-05-08 16:01:09</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>46150.66443287037</v>
+        <v>46150.66746527778</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1218,39 +1279,44 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>DIABATE ABDOULAYE</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>02:10:56</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>02:22:55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AC981</t>
+          <t>AC333</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SANDEGUE</t>
+          <t>DJEDA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AC981</t>
+          <t>AC333_1800</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>ABBSC01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1260,11 +1326,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-05-08 16:01:09</t>
+          <t>2026-05-08 16:08:30</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>46150.66746527778</v>
+        <v>46150.67256944445</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1273,44 +1339,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>02:06:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>02:15:34</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ET297</t>
+          <t>AC634</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TAOUDI</t>
+          <t>ABINADER</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ET297_900</t>
+          <t>AC634</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>BVBSC04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1320,11 +1391,11 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-05-08 16:01:09</t>
+          <t>2026-05-08 17:01:02</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>46150.66746527778</v>
+        <v>46150.70905092593</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1338,39 +1409,44 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>02:06:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>01:23:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ET284</t>
+          <t>AC535</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NAMASSI</t>
+          <t>SAGO</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ET284_900</t>
+          <t>AC535_900</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>YOBSC07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1380,11 +1456,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-05-08 16:01:09</t>
+          <t>2026-05-08 17:31:34</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>46150.66746527778</v>
+        <v>46150.73025462963</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1398,39 +1474,44 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>N'CHO ACHY MARC OLIVIER</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>02:06:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>00:52:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ET285</t>
+          <t>AC673</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>YOROBODI</t>
+          <t>GESCO_HEVEA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ET285_900</t>
+          <t>AC673_1800</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1440,11 +1521,11 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-05-08 16:01:09</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>46150.66746527778</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1453,44 +1534,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>02:06:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AC758</t>
+          <t>AC671</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KOUASSI_DATEKRO</t>
+          <t>YATSEKOI</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AC758</t>
+          <t>AC671_900</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AGBSC22</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1500,11 +1586,11 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-05-08 16:01:09</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>46150.66746527778</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1518,39 +1604,44 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>EKI AKA ADJIRI MARC</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>02:06:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AC333</t>
+          <t>ET543</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJEDA</t>
+          <t>YOP_GESCO_BONIKRO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AC333_1800</t>
+          <t>ET543_900</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ABBSC01</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1560,11 +1651,11 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-05-08 16:08:30</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>46150.67256944445</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1578,34 +1669,39 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>01:59:13</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AC752</t>
+          <t>AC727</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KOYEKRO</t>
+          <t>GESCO_FOURIERE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AC752_900</t>
+          <t>AC727_900</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SIBSC08</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1620,11 +1716,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-05-08 16:51:39</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>46150.70253472222</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,44 +1729,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>EKI AKA ADJIRI MARC</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>01:16:04</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AC965</t>
+          <t>ET543</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIOGOBOUA</t>
+          <t>YOP_GESCO_BONIKRO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AC965_900</t>
+          <t>ET543_1800</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SIBSC08</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1680,11 +1781,11 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-05-08 16:53:09</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>46150.70357638889</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1693,39 +1794,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>KONATE BAZOUMANA</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>01:14:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AC628</t>
+          <t>AC671</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MICAO</t>
+          <t>YATSEKOI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AC628_1800</t>
+          <t>AC671_1800</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SIBSC08</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1740,11 +1846,11 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-05-08 16:57:09</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>46150.70635416666</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1763,48 +1869,53 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>01:10:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ET694</t>
+          <t>AC314</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PBOUET_CITE_GRACE</t>
+          <t>GESCO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ET694</t>
+          <t>AC314_900</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-05-07 15:35:00</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>46149.64930555555</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1813,58 +1924,63 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>26:32:43</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ET535</t>
+          <t>AC673</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GONZAGUE_AIR_FRANCE</t>
+          <t>GESCO_HEVEA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ET535</t>
+          <t>AC673_900</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-05-07 15:35:02</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>46149.6493287037</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1873,58 +1989,63 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>26:32:41</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ET327</t>
+          <t>AC727</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PETITE_BAIE</t>
+          <t>GESCO_FOURIERE</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ET327</t>
+          <t>AC727_1800</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-05-08 11:34:55</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>46150.48258101852</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,53 +2059,58 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>06:32:48</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AC858</t>
+          <t>AC314</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DOBA</t>
+          <t>GESCO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AC858</t>
+          <t>AC314_1800</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>SIBSC05</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-05-08 15:10:14</t>
+          <t>2026-05-08 17:40:29</t>
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>46150.63210648148</v>
+        <v>46150.73644675926</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1998,53 +2124,58 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>02:57:29</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>00:43:35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AC865</t>
+          <t>ET487</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LOBOGBA</t>
+          <t>ZUZUOKO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AC865</t>
+          <t>ET487</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>YOBSC07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>BTS OUTAGE HUA</t>
+          <t>BTS OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-05-08 15:19:01</t>
+          <t>2026-05-08 17:56:04</t>
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>46150.63820601852</v>
+        <v>46150.74726851852</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2053,44 +2184,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>N'CHO ACHY MARC OLIVIER</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>02:48:42</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>00:28:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AC503</t>
+          <t>ET327</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MINIGNAN</t>
+          <t>PETITE_BAIE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AC503</t>
+          <t>ET327</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>GBMBSC14</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2100,11 +2236,11 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-05-08 15:25:03</t>
+          <t>2026-05-08 11:34:55</t>
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>46150.64239583333</v>
+        <v>46150.48258101852</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2118,39 +2254,44 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>02:42:40</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>06:49:09</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AC870</t>
+          <t>AC865</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MASSADOUGOU</t>
+          <t>LOBOGBA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AC870</t>
+          <t>AC865</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>YAMBSC12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2160,11 +2301,11 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-05-08 15:42:48</t>
+          <t>2026-05-08 15:19:01</t>
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>46150.65472222222</v>
+        <v>46150.63820601852</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2173,17 +2314,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>02:24:55</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>03:05:03</t>
         </is>
       </c>
     </row>
@@ -2243,24 +2389,29 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>01:33:05</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>01:49:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>IM289</t>
+          <t>ET594</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KOLIKO</t>
+          <t>NIAKARA_CHATEAU</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IM289</t>
+          <t>ET594</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2270,7 +2421,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2280,11 +2431,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-05-08 16:36:40</t>
+          <t>2026-05-08 16:55:23</t>
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>46150.69560185185</v>
+        <v>46150.70512731482</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2298,39 +2449,44 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>01:26:03</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>01:28:41</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AC421</t>
+          <t>IM167</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>YAM_BARRAGE</t>
+          <t>KANANGONON</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AC421</t>
+          <t>IM167</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>BKMBSC15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2340,11 +2496,11 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-05-08 16:52:07</t>
+          <t>2026-05-08 17:13:33</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46150.7028587963</v>
+        <v>46150.71774305555</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2358,39 +2514,44 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>01:15:36</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>01:10:31</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ET473</t>
+          <t>AC701</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>OUANADIEKAHA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ET473</t>
+          <t>AC701</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>BKMBSC15</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2400,11 +2561,11 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-05-08 16:52:13</t>
+          <t>2026-05-08 17:13:35</t>
         </is>
       </c>
       <c r="H33" s="3" t="n">
-        <v>46150.70292824074</v>
+        <v>46150.71776620371</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2413,39 +2574,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>01:15:30</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>01:10:29</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ET594</t>
+          <t>ET781</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NIAKARA_CHATEAU</t>
+          <t>DARAKOKAHA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ET594</t>
+          <t>ET781</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>BKMBSC15</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2460,11 +2626,11 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-05-08 16:55:23</t>
+          <t>2026-05-08 17:13:35</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>46150.70512731482</v>
+        <v>46150.71776620371</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2483,24 +2649,29 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>01:12:20</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>01:10:29</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IM184</t>
+          <t>ET852</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KPADAGNOA</t>
+          <t>TRAWAININKRO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IM184</t>
+          <t>ET852</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2515,16 +2686,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-05-08 16:34:34</t>
+          <t>2026-05-08 17:21:19</t>
         </is>
       </c>
       <c r="H35" s="3" t="n">
-        <v>46150.6906712963</v>
+        <v>46150.72319444444</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2538,53 +2709,58 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>KONATE BAZOUMANA</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>01:33:09</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>01:02:40</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IM429</t>
+          <t>ET613</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GADAGO_RURAL</t>
+          <t>LUEHOUAN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IM429</t>
+          <t>ET613</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>DAMBSC13</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>DALOA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSL Fault</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-05-08 16:58:09</t>
+          <t>2026-05-08 17:53:50</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>46150.70704861111</v>
+        <v>46150.7457175926</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2593,57 +2769,67 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>ASSIE N'GUESSAN FRANCOIS</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>01:09:34</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>00:30:14</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AC919</t>
+          <t>ET125</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FORUM_NORD</t>
+          <t>KOREGUHE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BB_AC919_GL</t>
+          <t>ET125</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ENODEB OUTAGE ERIC</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-05-08 08:57:28</t>
+          <t>2026-05-08 17:54:05</t>
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>46150.37657407407</v>
+        <v>46150.7458912037</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2653,112 +2839,127 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>09:05:27</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>00:29:59</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ET937</t>
+          <t>AC449</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ADJAME_DJIBI</t>
+          <t>BUYO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BB_ET937_GL</t>
+          <t>AC449</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ENODEB OUTAGE ERIC</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-05-08 08:57:28</t>
+          <t>2026-05-08 17:57:12</t>
         </is>
       </c>
       <c r="H38" s="3" t="n">
-        <v>46150.37324074074</v>
+        <v>46150.74805555555</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>09:10:15</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>00:26:52</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ET473</t>
+          <t>ET354</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>BUYO_RESIDENTIEL</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LET473</t>
+          <t>ET354</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>DAMBSC13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ENODEB OUTAGE HUA</t>
+          <t>BTS OUTAGE HUA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-05-08 16:24:43</t>
+          <t>2026-05-08 17:57:13</t>
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>46150.68386574074</v>
+        <v>46150.74806712963</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2768,57 +2969,62 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>01:42:57</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>00:26:51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ET943</t>
+          <t>IM184</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ATTECOUBE_OPERA</t>
+          <t>KPADAGNOA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BB_ET943_W</t>
+          <t>IM184</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>YAMBSC12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>CSL Fault</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-05-08 03:41:27</t>
+          <t>2026-05-08 16:34:34</t>
         </is>
       </c>
       <c r="H40" s="3" t="n">
-        <v>46150.15378472222</v>
+        <v>46150.6906712963</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2828,52 +3034,62 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>KONATE BAZOUMANA</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>14:26:16</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>01:49:30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ET943</t>
+          <t>IM412</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ATTECOUBE_OPERA</t>
+          <t>RURAL_FARAKO-KORO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BB_ET943_GL</t>
+          <t>IM412</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>KOMBSC16</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>KORHOGO</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>CSL Fault</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-05-08 03:41:53</t>
+          <t>2026-05-08 17:26:30</t>
         </is>
       </c>
       <c r="H41" s="3" t="n">
-        <v>46150.15408564815</v>
+        <v>46150.72673611111</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2883,52 +3099,62 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>14:25:50</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>00:57:34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AC331</t>
+          <t>IM429</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AGBAN_VILLAGE</t>
+          <t>GADAGO_RURAL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BB_AC331_GL</t>
+          <t>IM429</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>CSL Fault</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-05-08 08:16:25</t>
+          <t>2026-05-08 17:44:16</t>
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>46150.34473379629</v>
+        <v>46150.73907407407</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>2G</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2938,34 +3164,34 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>09:51:18</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>00:39:48</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AC331</t>
+          <t>AC919</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AGBAN_VILLAGE</t>
+          <t>FORUM_NORD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BB_AC331_W</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>ABRNC01_RadioNode</t>
+          <t>BB_AC919_GL</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2975,20 +3201,20 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-05-08 08:16:52</t>
+          <t>2026-05-08 08:57:28</t>
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>46150.34504629629</v>
+        <v>46150.37657407407</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3003,29 +3229,29 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>09:50:51</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>09:21:48</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ET019</t>
+          <t>ET937</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BLACK_MARKET</t>
+          <t>ADJAME_DJIBI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>WET019</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>ABRNC01_GROUP</t>
+          <t>BB_ET937_GL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3035,20 +3261,20 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-05-08 09:03:03</t>
+          <t>2026-05-08 08:57:28</t>
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>46150.37711805556</v>
+        <v>46150.37324074074</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3063,47 +3289,57 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>09:04:40</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>09:26:36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ET019</t>
+          <t>ET473</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BLACK_MARKET</t>
+          <t>FONDI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BB_ET019_GL</t>
+          <t>LET473</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>FONDI</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>YAMOUSSOUKRO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Heartbeat Failure</t>
+          <t>ENODEB OUTAGE HUA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-05-08 09:04:24</t>
+          <t>2026-05-08 17:29:01</t>
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>46150.37805555556</v>
+        <v>46150.72851851852</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3113,34 +3349,39 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>LALLIER DIDIER</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>09:03:19</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>00:55:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ET795</t>
+          <t>ET943</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NEW_MISSION_LIBANAISE</t>
+          <t>ATTECOUBE_OPERA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BB_ET795_W</t>
+          <t>BB_ET943_W</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MARNC21_RadioNode</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3155,11 +3396,11 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-05-08 09:04:58</t>
+          <t>2026-05-08 03:41:27</t>
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>46150.37844907407</v>
+        <v>46150.15378472222</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3178,24 +3419,29 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>09:02:45</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>14:42:37</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ET795</t>
+          <t>ET943</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NEW_MISSION_LIBANAISE</t>
+          <t>ATTECOUBE_OPERA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BB_ET795_GL</t>
+          <t>BB_ET943_GL</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3210,11 +3456,11 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-05-08 09:06:53</t>
+          <t>2026-05-08 03:41:53</t>
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>46150.37978009259</v>
+        <v>46150.15408564815</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3233,24 +3479,29 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>09:00:50</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>14:42:11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ET413</t>
+          <t>AC331</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ADJAME_ROXY</t>
+          <t>AGBAN_VILLAGE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BB_ET413_GL</t>
+          <t>BB_AC331_GL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3265,11 +3516,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-05-08 11:21:06</t>
+          <t>2026-05-08 08:16:25</t>
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>46150.47298611111</v>
+        <v>46150.34473379629</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3288,24 +3539,29 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>06:46:37</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>10:07:39</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ET790</t>
+          <t>AC331</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ADJAME_FORUM</t>
+          <t>AGBAN_VILLAGE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BB_ET790_W</t>
+          <t>BB_AC331_W</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3325,11 +3581,11 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-05-08 11:21:21</t>
+          <t>2026-05-08 08:16:52</t>
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>46150.47315972222</v>
+        <v>46150.34504629629</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3348,24 +3604,34 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>06:46:22</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>10:07:12</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ET790</t>
+          <t>ET019</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ADJAME_FORUM</t>
+          <t>BLACK_MARKET</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BB_ET790_GL</t>
+          <t>WET019</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ABRNC01_GROUP</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3380,15 +3646,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-05-08 11:21:26</t>
+          <t>2026-05-08 09:03:03</t>
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>46150.47321759259</v>
+        <v>46150.37711805556</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3403,29 +3669,29 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>06:46:17</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>09:21:01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ET413</t>
+          <t>ET019</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ADJAME_ROXY</t>
+          <t>BLACK_MARKET</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BB_ET413_W</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ABRNC01_RadioNode</t>
+          <t>BB_ET019_GL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3440,15 +3706,15 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-05-08 11:21:38</t>
+          <t>2026-05-08 09:04:24</t>
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>46150.47335648148</v>
+        <v>46150.37805555556</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3463,24 +3729,34 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>06:46:05</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>09:19:40</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ET433</t>
+          <t>ET795</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ADJAME_EMU_EBENEZER</t>
+          <t>NEW_MISSION_LIBANAISE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BB_ET433_GL</t>
+          <t>BB_ET795_W</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MARNC21_RadioNode</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3495,15 +3771,15 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-05-08 12:34:52</t>
+          <t>2026-05-08 09:04:58</t>
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>46150.52421296296</v>
+        <v>46150.37844907407</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3518,29 +3794,29 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>05:32:51</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>09:19:06</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ET433</t>
+          <t>ET795</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ADJAME_EMU_EBENEZER</t>
+          <t>NEW_MISSION_LIBANAISE</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BB_ET433_W</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ABRNC01</t>
+          <t>BB_ET795_GL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3555,15 +3831,15 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-05-08 12:36:02</t>
+          <t>2026-05-08 09:06:53</t>
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>46150.52502314815</v>
+        <v>46150.37978009259</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3578,34 +3854,34 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>05:31:41</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>09:17:11</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ET425</t>
+          <t>ET413</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>KOUWEIT_PIERRE_GADIE</t>
+          <t>ADJAME_ROXY</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BB_ET425_W</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SIRNC05_RadioNode</t>
+          <t>BB_ET413_GL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3615,15 +3891,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-05-08 14:41:07</t>
+          <t>2026-05-08 11:21:06</t>
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>46150.61188657407</v>
+        <v>46150.47298611111</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3633,34 +3909,44 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>TOURE HABIB ARMEL</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>03:26:36</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>07:02:58</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ET425</t>
+          <t>ET790</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KOUWEIT_PIERRE_GADIE</t>
+          <t>ADJAME_FORUM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BB_ET425_GL</t>
+          <t>BB_ET790_W</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ABRNC01_RadioNode</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3670,15 +3956,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2026-05-08 14:41:14</t>
+          <t>2026-05-08 11:21:21</t>
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>46150.61196759259</v>
+        <v>46150.47315972222</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3688,34 +3974,39 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>TOURE HABIB ARMEL</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>03:26:29</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>07:02:43</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AC703</t>
+          <t>ET790</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CARREFOUR_CHU</t>
+          <t>ADJAME_FORUM</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BB_AC703_GL</t>
+          <t>BB_ET790_GL</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3725,11 +4016,11 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2026-05-08 15:31:29</t>
+          <t>2026-05-08 11:21:26</t>
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>46150.64686342593</v>
+        <v>46150.47321759259</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3743,39 +4034,44 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>GNAORE DIDI ERIC</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>02:36:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>07:02:38</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AC703</t>
+          <t>ET413</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CARREFOUR_CHU</t>
+          <t>ADJAME_ROXY</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BB_AC703_W</t>
+          <t>BB_ET413_W</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SIRNC05_RadioNode</t>
+          <t>ABRNC01_RadioNode</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3785,11 +4081,11 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026-05-08 15:32:12</t>
+          <t>2026-05-08 11:21:38</t>
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>46150.64736111111</v>
+        <v>46150.47335648148</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3803,39 +4099,39 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>GNAORE DIDI ERIC</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>02:35:31</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>07:02:26</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AC785</t>
+          <t>ET433</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GROBONOU_DAN</t>
+          <t>ADJAME_EMU_EBENEZER</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WAC785</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>SIRNC08_GROUP</t>
+          <t>BB_ET433_GL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3845,57 +4141,62 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2026-05-08 16:00:08</t>
+          <t>2026-05-08 12:34:52</t>
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>46150.66675925926</v>
+        <v>46150.52421296296</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>02:07:35</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>05:49:12</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AC758</t>
+          <t>ET433</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>KOUASSI_DATEKRO</t>
+          <t>ADJAME_EMU_EBENEZER</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WAC758</t>
+          <t>BB_ET433_W</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AGRNC22_GROUP</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3905,11 +4206,11 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-05-08 16:00:57</t>
+          <t>2026-05-08 12:36:02</t>
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>46150.66732638889</v>
+        <v>46150.52502314815</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3918,44 +4219,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>02:06:46</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>05:48:02</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AC981</t>
+          <t>ET425</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SANDEGUE</t>
+          <t>KOUWEIT_PIERRE_GADIE</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WAC981</t>
+          <t>BB_ET425_W</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AGRNC22_GROUP</t>
+          <t>SIRNC05_RadioNode</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3965,11 +4271,11 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-05-08 16:00:58</t>
+          <t>2026-05-08 14:41:07</t>
         </is>
       </c>
       <c r="H60" s="3" t="n">
-        <v>46150.66733796296</v>
+        <v>46150.61188657407</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3978,39 +4284,44 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>02:06:45</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>03:42:57</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ET626</t>
+          <t>ET425</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DIMANDOUGOU</t>
+          <t>KOUWEIT_PIERRE_GADIE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BB_ET626_GL</t>
+          <t>BB_ET425_GL</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4020,11 +4331,11 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-05-08 16:03:27</t>
+          <t>2026-05-08 14:41:14</t>
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>46150.6690625</v>
+        <v>46150.61196759259</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4038,34 +4349,39 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>02:04:16</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>03:42:50</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AC981</t>
+          <t>AC703</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SANDEGUE</t>
+          <t>CARREFOUR_CHU</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BB_AC981_GL</t>
+          <t>BB_AC703_GL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4075,11 +4391,11 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-05-08 16:03:53</t>
+          <t>2026-05-08 15:31:29</t>
         </is>
       </c>
       <c r="H62" s="3" t="n">
-        <v>46150.66936342593</v>
+        <v>46150.64686342593</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4088,44 +4404,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>02:03:50</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>02:52:35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ET285</t>
+          <t>AC703</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>YOROBODI</t>
+          <t>CARREFOUR_CHU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BB_ET285_W</t>
+          <t>BB_AC703_W</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>AGRNC22_RadioNode</t>
+          <t>SIRNC05_RadioNode</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4135,11 +4456,11 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:02</t>
+          <t>2026-05-08 15:32:12</t>
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>46150.66946759259</v>
+        <v>46150.64736111111</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4153,34 +4474,39 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>02:03:41</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>02:51:52</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ET626</t>
+          <t>AC758</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DIMANDOUGOU</t>
+          <t>KOUASSI_DATEKRO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BB_ET626_W</t>
+          <t>WAC758</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>AGRNC22_RadioNode</t>
+          <t>AGRNC22_GROUP</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4195,11 +4521,11 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:17</t>
+          <t>2026-05-08 16:00:57</t>
         </is>
       </c>
       <c r="H64" s="3" t="n">
-        <v>46150.66964120371</v>
+        <v>46150.66732638889</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4208,7 +4534,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -4218,29 +4544,29 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>02:03:26</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>02:23:07</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ET297</t>
+          <t>AC758</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TAOUDI</t>
+          <t>KOUASSI_DATEKRO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>BB_ET297_W</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>AGRNC22</t>
+          <t>BB_AC758_GL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4255,20 +4581,20 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:28</t>
+          <t>2026-05-08 16:05:31</t>
         </is>
       </c>
       <c r="H65" s="3" t="n">
-        <v>46150.66976851852</v>
+        <v>46150.67049768518</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -4278,29 +4604,39 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>02:03:15</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>02:18:33</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IM300</t>
+          <t>AC333</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BANDAKAGNI-TOMORA</t>
+          <t>DJEDA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BB_IM300_L</t>
+          <t>BB_AC333_W</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ABRNC01_RadioNode</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4310,15 +4646,15 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:30</t>
+          <t>2026-05-08 16:11:20</t>
         </is>
       </c>
       <c r="H66" s="3" t="n">
-        <v>46150.66979166667</v>
+        <v>46150.67453703703</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4328,34 +4664,39 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>02:03:13</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>02:12:44</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ET284</t>
+          <t>AC333</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NAMASSI</t>
+          <t>DJEDA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BB_ET284_GL</t>
+          <t>BB_AC333_GL</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4365,11 +4706,11 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:32</t>
+          <t>2026-05-08 16:11:56</t>
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>46150.66981481481</v>
+        <v>46150.6749537037</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4383,39 +4724,44 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>02:03:11</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>02:12:08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ET284</t>
+          <t>ET524</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NAMASSI</t>
+          <t>ADJAME_CHATEAU</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BB_ET284_W</t>
+          <t>BB_ET524_W</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
+          <t>ABRNC01_RadioNode</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4425,11 +4771,11 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-05-08 16:04:57</t>
+          <t>2026-05-08 16:13:30</t>
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>46150.67010416667</v>
+        <v>46150.67604166667</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4438,39 +4784,44 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>02:02:46</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>02:10:34</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ET285</t>
+          <t>ET524</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>YOROBODI</t>
+          <t>ADJAME_CHATEAU</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>BB_ET285_GL</t>
+          <t>BB_ET524_GL</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4480,11 +4831,11 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05:14</t>
+          <t>2026-05-08 16:13:50</t>
         </is>
       </c>
       <c r="H69" s="3" t="n">
-        <v>46150.67030092593</v>
+        <v>46150.67627314815</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4493,44 +4844,44 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>02:02:29</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>02:10:14</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IM300</t>
+          <t>IM011</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BANDAKAGNI-TOMORA</t>
+          <t>KOBAKRO_ISRAEL</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>BB_IM300_GW</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>BVRNC04</t>
+          <t>BB_IM011_L</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4540,15 +4891,15 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05:17</t>
+          <t>2026-05-08 16:35:33</t>
         </is>
       </c>
       <c r="H70" s="3" t="n">
-        <v>46150.67033564814</v>
+        <v>46150.69135416667</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4558,34 +4909,44 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>02:02:26</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>01:48:31</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AC758</t>
+          <t>IM011</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KOUASSI_DATEKRO</t>
+          <t>KOBAKRO_ISRAEL</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BB_AC758_GL</t>
+          <t>BB_IM011_GW</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4595,52 +4956,62 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05:31</t>
+          <t>2026-05-08 16:35:33</t>
         </is>
       </c>
       <c r="H71" s="3" t="n">
-        <v>46150.67049768518</v>
+        <v>46150.69135416667</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>02:02:12</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>01:48:31</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ET297</t>
+          <t>AC634</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TAOUDI</t>
+          <t>ABINADER</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>BB_ET297_GL</t>
+          <t>BB_AC634_W</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BVRNC04_RadioNode</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4650,15 +5021,15 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-05-08 16:05:42</t>
+          <t>2026-05-08 17:04:32</t>
         </is>
       </c>
       <c r="H72" s="3" t="n">
-        <v>46150.670625</v>
+        <v>46150.71148148148</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -4668,34 +5039,34 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>02:02:01</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>01:19:32</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AC333</t>
+          <t>AC634</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>DJEDA</t>
+          <t>ABINADER</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BB_AC333_W</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ABRNC01_RadioNode</t>
+          <t>BB_AC634_GL</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4710,15 +5081,15 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:20</t>
+          <t>2026-05-08 17:04:33</t>
         </is>
       </c>
       <c r="H73" s="3" t="n">
-        <v>46150.67453703703</v>
+        <v>46150.71149305555</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -4728,34 +5099,44 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>01:56:23</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>01:19:31</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AC333</t>
+          <t>AC314</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DJEDA</t>
+          <t>GESCO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BB_AC333_GL</t>
+          <t>WAC314</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SIRNC05_GROUP</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4765,57 +5146,62 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2026-05-08 16:11:56</t>
+          <t>2026-05-08 17:42:10</t>
         </is>
       </c>
       <c r="H74" s="3" t="n">
-        <v>46150.6749537037</v>
+        <v>46150.73761574074</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>01:55:47</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>00:41:54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ET524</t>
+          <t>AC673</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ADJAME_CHATEAU</t>
+          <t>GESCO_HEVEA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BB_ET524_W</t>
+          <t>WAC673</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ABRNC01_RadioNode</t>
+          <t>SIRNC05_GROUP</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4825,11 +5211,11 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-05-08 16:13:30</t>
+          <t>2026-05-08 17:42:24</t>
         </is>
       </c>
       <c r="H75" s="3" t="n">
-        <v>46150.67604166667</v>
+        <v>46150.73777777778</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4843,34 +5229,44 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>01:54:13</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>00:41:40</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ET524</t>
+          <t>ET543</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ADJAME_CHATEAU</t>
+          <t>YOP_GESCO_BONIKRO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BB_ET524_GL</t>
+          <t>BB_ET543_W</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SIRNC05_RadioNode</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4880,52 +5276,57 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-05-08 16:13:50</t>
+          <t>2026-05-08 17:44:14</t>
         </is>
       </c>
       <c r="H76" s="3" t="n">
-        <v>46150.67627314815</v>
+        <v>46150.73905092593</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>01:53:53</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>00:39:50</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IM011</t>
+          <t>AC673</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KOBAKRO_ISRAEL</t>
+          <t>GESCO_HEVEA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BB_IM011_L</t>
+          <t>BB_AC673_GL</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4935,57 +5336,57 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35:33</t>
+          <t>2026-05-08 17:44:18</t>
         </is>
       </c>
       <c r="H77" s="3" t="n">
-        <v>46150.69135416667</v>
+        <v>46150.73909722222</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>01:32:10</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>00:39:46</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IM011</t>
+          <t>AC727</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KOBAKRO_ISRAEL</t>
+          <t>GESCO_FOURIERE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BB_IM011_GW</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>AORNC06</t>
+          <t>BB_AC727_GL</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4995,15 +5396,15 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35:33</t>
+          <t>2026-05-08 17:45:23</t>
         </is>
       </c>
       <c r="H78" s="3" t="n">
-        <v>46150.69135416667</v>
+        <v>46150.73984953704</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5013,117 +5414,117 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>01:32:10</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>00:38:41</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ET535</t>
+          <t>AC314</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GONZAGUE_AIR_FRANCE</t>
+          <t>GESCO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GONZAG_AIR_FRANCE</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>GONZAG_AIR_FRANCE</t>
+          <t>BB_AC314_GL</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-05-07 15:38:29</t>
+          <t>2026-05-08 17:45:52</t>
         </is>
       </c>
       <c r="H79" s="3" t="n">
-        <v>46149.65172453703</v>
+        <v>46150.74018518518</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>26:29:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>00:38:12</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ET694</t>
+          <t>ET543</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>PBOUET_CITE_GRACE</t>
+          <t>YOP_GESCO_BONIKRO</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PBOUET_CITE_GRACE</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>PBOUET_CITE_GRACE</t>
+          <t>BB_ET543_GL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-05-07 15:38:29</t>
+          <t>2026-05-08 17:45:52</t>
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>46149.65172453703</v>
+        <v>46150.74018518518</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5133,57 +5534,62 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>26:29:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>00:38:12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ET327</t>
+          <t>AC727</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PETITE_BAIE</t>
+          <t>GESCO_FOURIERE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PETITE_BAIE</t>
+          <t>BB_AC727_W</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PETITE_BAIE</t>
+          <t>SIRNC05_RadioNode</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-05-08 11:37:54</t>
+          <t>2026-05-08 17:46:18</t>
         </is>
       </c>
       <c r="H81" s="3" t="n">
-        <v>46150.48465277778</v>
+        <v>46150.74048611111</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5193,177 +5599,182 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>06:29:49</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>00:37:46</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AC858</t>
+          <t>IM006</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>DOBA</t>
+          <t>DIOULABOUGOU</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DOBA</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>DOBA</t>
+          <t>BB_IM006_L</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-05-08 15:13:30</t>
+          <t>2026-05-08 17:53:51</t>
         </is>
       </c>
       <c r="H82" s="3" t="n">
-        <v>46150.634375</v>
+        <v>46150.74572916667</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>4G</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>ADOU ANDRE YAO</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>02:54:13</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>00:30:13</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AC865</t>
+          <t>IM006</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LOBOGBA</t>
+          <t>DIOULABOUGOU</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LOGOGBA</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>LOGOGBA</t>
+          <t>BB_IM006_GW</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2026-05-08 15:22:13</t>
+          <t>2026-05-08 17:54:19</t>
         </is>
       </c>
       <c r="H83" s="3" t="n">
-        <v>46150.64042824074</v>
+        <v>46150.74605324074</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,3G</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>ADOU ANDRE YAO</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>02:45:30</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>00:29:45</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>AC870</t>
+          <t>AC995</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MASSADOUGOU</t>
+          <t>PHRCIE_ACADJOBA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MASSADOUGOU</t>
+          <t>WAC995</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>MASSADOUGOU</t>
+          <t>SIRNC05_GROUP</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2026-05-08 15:46:19</t>
+          <t>2026-05-08 17:55:47</t>
         </is>
       </c>
       <c r="H84" s="3" t="n">
-        <v>46150.65716435185</v>
+        <v>46150.74707175926</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>3G</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5373,57 +5784,57 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>02:21:24</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>00:28:17</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IM184</t>
+          <t>AC995</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>KPADAGNOA</t>
+          <t>PHRCIE_ACADJOBA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>KPADAGNOA_R</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>KPADAGNOA_R</t>
+          <t>BB_AC995_GL</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NE Is Disconnected</t>
+          <t>Heartbeat Failure</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2026-05-08 16:37:58</t>
+          <t>2026-05-08 17:57:35</t>
         </is>
       </c>
       <c r="H85" s="3" t="n">
-        <v>46150.69303240741</v>
+        <v>46150.74832175926</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2G,3G,4G</t>
+          <t>2G,4G</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5433,39 +5844,44 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>KONATE BAZOUMANA</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>01:29:45</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>00:26:29</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ET620</t>
+          <t>ET327</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GODELILIE</t>
+          <t>PETITE_BAIE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>GODELILIE</t>
+          <t>PETITE_BAIE</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>GODELILIE</t>
+          <t>PETITE_BAIE</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -5475,11 +5891,11 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2026-05-08 16:38:06</t>
+          <t>2026-05-08 11:37:54</t>
         </is>
       </c>
       <c r="H86" s="3" t="n">
-        <v>46150.693125</v>
+        <v>46150.48465277778</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -5493,39 +5909,44 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>KONATE BAZOUMANA</t>
+          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>01:29:37</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>06:46:10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IM289</t>
+          <t>AC865</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>KOLIKO</t>
+          <t>LOBOGBA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>KOLIKO</t>
+          <t>LOGOGBA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KOLIKO</t>
+          <t>LOGOGBA</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -5535,11 +5956,11 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2026-05-08 16:44:58</t>
+          <t>2026-05-08 15:22:13</t>
         </is>
       </c>
       <c r="H87" s="3" t="n">
-        <v>46150.69789351852</v>
+        <v>46150.64042824074</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5548,44 +5969,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>01:22:45</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>03:01:51</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AC421</t>
+          <t>IM184</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>YAM_BARRAGE</t>
+          <t>KPADAGNOA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>YAM_BARRAGE</t>
+          <t>KPADAGNOA_R</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>YAM_BARRAGE</t>
+          <t>KPADAGNOA_R</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -5595,11 +6021,11 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2026-05-08 16:55:17</t>
+          <t>2026-05-08 16:37:58</t>
         </is>
       </c>
       <c r="H88" s="3" t="n">
-        <v>46150.70505787037</v>
+        <v>46150.69303240741</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5613,39 +6039,44 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>KONATE BAZOUMANA</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>01:12:26</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>01:46:06</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ET473</t>
+          <t>ET620</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>GODELILIE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>GODELILIE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>GODELILIE</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5655,11 +6086,11 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2026-05-08 16:55:17</t>
+          <t>2026-05-08 16:38:06</t>
         </is>
       </c>
       <c r="H89" s="3" t="n">
-        <v>46150.70505787037</v>
+        <v>46150.693125</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -5673,39 +6104,44 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>KONATE BAZOUMANA</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>01:12:26</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>01:45:58</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ET594</t>
+          <t>IM289</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NIAKARA_CHATEAU</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NIAKARA_CHATEAU</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NIAKARA_CHATEAU</t>
+          <t>KOLIKO</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>MAN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5715,11 +6151,11 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>2026-05-08 16:58:19</t>
+          <t>2026-05-08 16:44:58</t>
         </is>
       </c>
       <c r="H90" s="3" t="n">
-        <v>46150.70716435185</v>
+        <v>46150.69789351852</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5733,57 +6169,62 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>01:09:24</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>01:39:06</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AC007</t>
+          <t>ET594</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>COMAF</t>
+          <t>NIAKARA_CHATEAU</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>WAC007</t>
+          <t>NIAKARA_CHATEAU</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>MARNC21</t>
+          <t>NIAKARA_CHATEAU</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2026-05-07 16:16:18</t>
+          <t>2026-05-08 16:58:19</t>
         </is>
       </c>
       <c r="H91" s="3" t="n">
-        <v>46149.72067129629</v>
+        <v>46150.70716435185</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -5793,57 +6234,62 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>24:49:57</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>01:25:45</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ET943</t>
+          <t>IM167</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ATTECOUBE_OPERA</t>
+          <t>KANANGONON</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BB_ET943_W</t>
+          <t>KANANGONON</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>KANANGONON</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2026-05-08 03:42:32</t>
+          <t>2026-05-08 17:16:51</t>
         </is>
       </c>
       <c r="H92" s="3" t="n">
-        <v>46150.15453703704</v>
+        <v>46150.72003472222</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -5853,57 +6299,62 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>14:25:11</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>01:07:13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AC919</t>
+          <t>ET781</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FORUM_NORD</t>
+          <t>DARAKOKAHA</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BB_AC919_W</t>
+          <t>DARAKOKAHA</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>DARAKOKAHA</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2026-05-08 08:58:55</t>
+          <t>2026-05-08 17:16:51</t>
         </is>
       </c>
       <c r="H93" s="3" t="n">
-        <v>46150.37769675926</v>
+        <v>46150.72003472222</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -5913,117 +6364,127 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>09:03:50</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>01:07:13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ET795</t>
+          <t>AC701</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>NEW_MISSION_LIBANAISE</t>
+          <t>OUANADIEKAHA</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BB_ET795_W</t>
+          <t>OUANADIEKAHA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>MARNC21</t>
+          <t>OUANADIEKAHA</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>BOUAKE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>2026-05-08 08:58:55</t>
+          <t>2026-05-08 17:16:58</t>
         </is>
       </c>
       <c r="H94" s="3" t="n">
-        <v>46150.37424768518</v>
+        <v>46150.72011574074</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>KOUAKOU KOFFI JONATHAN</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>09:08:48</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>01:07:06</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ET937</t>
+          <t>ET852</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ADJAME_DJIBI</t>
+          <t>TRAWAININKRO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BB_ET937_W</t>
+          <t>TRAVAININKRO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>MARNC21</t>
+          <t>TRAVAININKRO</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2026-05-08 08:58:55</t>
+          <t>2026-05-08 17:24:34</t>
         </is>
       </c>
       <c r="H95" s="3" t="n">
-        <v>46150.37769675926</v>
+        <v>46150.72539351852</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -6033,57 +6494,62 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>09:03:50</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>00:59:30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ET517</t>
+          <t>IM412</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ADJAME RENAULT</t>
+          <t>RURAL_FARAKO-KORO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BB_ET517_W</t>
+          <t>FARAKO-KORO_R</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>FARAKO-KORO_R</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>KORHOGO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2026-05-08 09:05:20</t>
+          <t>2026-05-08 17:32:30</t>
         </is>
       </c>
       <c r="H96" s="3" t="n">
-        <v>46150.3787037037</v>
+        <v>46150.73090277778</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -6093,57 +6559,62 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>YEO DOSONGUY ABRAHAM</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>09:02:23</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>00:51:34</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ET413</t>
+          <t>IM429</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ADJAME_ROXY</t>
+          <t>GADAGO_RURAL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>BB_ET413_W</t>
+          <t>GADAGO_R</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>GADAGO_R</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2026-05-08 11:16:27</t>
+          <t>2026-05-08 17:47:30</t>
         </is>
       </c>
       <c r="H97" s="3" t="n">
-        <v>46150.46975694445</v>
+        <v>46150.74131944445</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6153,117 +6624,127 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>06:51:16</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>00:36:34</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ET790</t>
+          <t>ET613</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ADJAME_FORUM</t>
+          <t>LUEHOUAN</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>BB_ET790_W</t>
+          <t>LUEHOUAN</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>LUEHOUAN</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>DALOA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2026-05-08 11:16:27</t>
+          <t>2026-05-08 17:56:51</t>
         </is>
       </c>
       <c r="H98" s="3" t="n">
-        <v>46150.46975694445</v>
+        <v>46150.7478125</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>ASSIE N'GUESSAN FRANCOIS</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>06:51:16</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>00:27:13</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ET433</t>
+          <t>ET125</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ADJAME_EMU_EBENEZER</t>
+          <t>KOREGUHE</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BB_ET433_W</t>
+          <t>KOREGUHE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ABRNC01</t>
+          <t>KOREGUHE</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ABIDJAN 03</t>
+          <t>GAGNOA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2026-05-08 12:30:12</t>
+          <t>2026-05-08 17:57:23</t>
         </is>
       </c>
       <c r="H99" s="3" t="n">
-        <v>46150.52097222222</v>
+        <v>46150.74818287037</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -6273,159 +6754,174 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>ABO EKPONON CLAUDE</t>
+          <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>05:37:31</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>00:26:41</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ET423</t>
+          <t>AC470</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>YOP_AGAYATE</t>
+          <t>TORTIYA</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BB_ET423_W</t>
+          <t>TORTIYA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>YORNC02</t>
+          <t>TORTIYA</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>KORHOGO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2026-05-08 14:35:36</t>
+          <t>2026-05-08 17:58:35</t>
         </is>
       </c>
       <c r="H100" s="3" t="n">
-        <v>46150.60805555555</v>
+        <v>46150.74901620371</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>TOURE HABIB ARMEL</t>
+          <t>KONE MOHAMED LAMINE</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>03:32:07</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>00:25:29</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>AC703</t>
+          <t>AC853</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>CARREFOUR_CHU</t>
+          <t>KADIOHA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>BB_AC703_W</t>
+          <t>KADIOHA</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SIRNC05</t>
+          <t>KADIOHA</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>KORHOGO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE ERIC</t>
+          <t>NE Is Disconnected</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2026-05-08 15:29:15</t>
+          <t>2026-05-08 17:59:30</t>
         </is>
       </c>
       <c r="H101" s="3" t="n">
-        <v>46150.6453125</v>
+        <v>46150.74965277778</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3G</t>
+          <t>2G,3G,4G</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>GNAORE DIDI ERIC</t>
+          <t>KONE MOHAMED LAMINE</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>02:38:28</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>00:24:34</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ET465</t>
+          <t>AC007</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GOMON3</t>
+          <t>COMAF</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BB_ET465_W</t>
+          <t>WAC007</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>SIRNC08</t>
+          <t>MARNC21</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>ABIDJAN 02</t>
+          <t>ABIDJAN 01</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6435,11 +6931,11 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2026-05-08 15:52:38</t>
+          <t>2026-05-07 16:16:18</t>
         </is>
       </c>
       <c r="H102" s="3" t="n">
-        <v>46150.67416666666</v>
+        <v>46149.72067129629</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6448,44 +6944,49 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>EKI AKA ADJIRI MARC</t>
+          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>01:56:55</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>25:06:18</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AC981</t>
+          <t>ET943</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SANDEGUE</t>
+          <t>ATTECOUBE_OPERA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>WAC981</t>
+          <t>BB_ET943_W</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -6495,11 +6996,11 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>2026-05-08 15:59:20</t>
+          <t>2026-05-08 03:42:32</t>
         </is>
       </c>
       <c r="H103" s="3" t="n">
-        <v>46150.6662037037</v>
+        <v>46150.15453703704</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6508,44 +7009,49 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>02:08:23</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>14:41:32</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AC785</t>
+          <t>AC919</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GROBONOU_DAN</t>
+          <t>FORUM_NORD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>WAC785</t>
+          <t>BB_AC919_W</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>YORNC02</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -6555,11 +7061,11 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>2026-05-08 16:02:52</t>
+          <t>2026-05-08 08:58:55</t>
         </is>
       </c>
       <c r="H104" s="3" t="n">
-        <v>46150.6686574074</v>
+        <v>46150.37769675926</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -6568,44 +7074,49 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>N'CHO ACHY MARC OLIVIER</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>02:04:51</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>09:20:11</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ET297</t>
+          <t>ET795</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TAOUDI</t>
+          <t>NEW_MISSION_LIBANAISE</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>BB_ET297_W</t>
+          <t>BB_ET795_W</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
+          <t>MARNC21</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6615,11 +7126,11 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2026-05-08 16:06:02</t>
+          <t>2026-05-08 08:58:55</t>
         </is>
       </c>
       <c r="H105" s="3" t="n">
-        <v>46150.67085648148</v>
+        <v>46150.37424768518</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6633,39 +7144,44 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>02:01:41</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>09:25:09</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ET285</t>
+          <t>ET937</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>YOROBODI</t>
+          <t>ADJAME_DJIBI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BB_ET285_W</t>
+          <t>BB_ET937_W</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
+          <t>MARNC21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6675,11 +7191,11 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2026-05-08 16:06:07</t>
+          <t>2026-05-08 08:58:55</t>
         </is>
       </c>
       <c r="H106" s="3" t="n">
-        <v>46150.67091435185</v>
+        <v>46150.37769675926</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -6693,39 +7209,44 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>02:01:36</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>09:20:11</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ET284</t>
+          <t>ET517</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NAMASSI</t>
+          <t>ADJAME RENAULT</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>BB_ET284_W</t>
+          <t>BB_ET517_W</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>AGRNC22</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>ABENGOUROU</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -6735,11 +7256,11 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>2026-05-08 16:06:10</t>
+          <t>2026-05-08 09:05:20</t>
         </is>
       </c>
       <c r="H107" s="3" t="n">
-        <v>46150.67094907408</v>
+        <v>46150.3787037037</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -6753,29 +7274,34 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>DIABATE ABDOULAYE</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>02:01:33</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>09:18:44</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AC333</t>
+          <t>ET413</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>DJEDA</t>
+          <t>ADJAME_ROXY</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BB_AC333_W</t>
+          <t>BB_ET413_W</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -6795,11 +7321,11 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>2026-05-08 16:07:27</t>
+          <t>2026-05-08 11:16:27</t>
         </is>
       </c>
       <c r="H108" s="3" t="n">
-        <v>46150.67184027778</v>
+        <v>46150.46975694445</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -6818,24 +7344,29 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>02:00:16</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>07:07:37</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ET524</t>
+          <t>ET790</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ADJAME_CHATEAU</t>
+          <t>ADJAME_FORUM</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>BB_ET524_W</t>
+          <t>BB_ET790_W</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6855,11 +7386,11 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>2026-05-08 16:07:29</t>
+          <t>2026-05-08 11:16:27</t>
         </is>
       </c>
       <c r="H109" s="3" t="n">
-        <v>46150.67186342592</v>
+        <v>46150.46975694445</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
@@ -6868,7 +7399,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -6878,34 +7409,39 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>02:00:14</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>07:07:37</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>IM011</t>
+          <t>ET433</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>KOBAKRO_ISRAEL</t>
+          <t>ADJAME_EMU_EBENEZER</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>BB_IM011_GW</t>
+          <t>BB_ET433_W</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>AORNC06</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ABIDJAN 04</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6915,11 +7451,11 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>2026-05-08 16:30:10</t>
+          <t>2026-05-08 12:30:12</t>
         </is>
       </c>
       <c r="H110" s="3" t="n">
-        <v>46150.68761574074</v>
+        <v>46150.52097222222</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -6933,34 +7469,39 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>COULIBALY ZIE ABOUBAKAR</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>01:37:33</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>05:53:52</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AC997</t>
+          <t>ET423</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>YOP_AMZA</t>
+          <t>YOP_AGAYATE</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>WAC997</t>
+          <t>BB_ET423_W</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>SIRNC05</t>
+          <t>YORNC02</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -6975,11 +7516,11 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2026-05-08 16:53:38</t>
+          <t>2026-05-08 14:35:36</t>
         </is>
       </c>
       <c r="H111" s="3" t="n">
-        <v>46150.70398148148</v>
+        <v>46150.60805555555</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -6993,53 +7534,58 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>GNAORE DIDI ERIC</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>01:13:59</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>03:48:28</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ET694</t>
+          <t>AC703</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PBOUET_CITE_GRACE</t>
+          <t>CARREFOUR_CHU</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>WET694</t>
+          <t>BB_AC703_W</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>SIRNC05</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>2026-05-07 15:33:39</t>
+          <t>2026-05-08 15:29:15</t>
         </is>
       </c>
       <c r="H112" s="3" t="n">
-        <v>46149.64836805555</v>
+        <v>46150.6453125</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -7053,53 +7599,58 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>OUATTARA PEFININ BRAHIMA</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>26:34:04</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>02:54:49</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ET535</t>
+          <t>AC333</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>GONZAGUE_AIR_FRANCE</t>
+          <t>DJEDA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>WET535</t>
+          <t>BB_AC333_W</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>2026-05-07 15:33:39</t>
+          <t>2026-05-08 16:07:27</t>
         </is>
       </c>
       <c r="H113" s="3" t="n">
-        <v>46149.64836805555</v>
+        <v>46150.67184027778</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -7113,53 +7664,58 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>26:34:04</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>02:16:37</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ET327</t>
+          <t>ET524</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PETITE_BAIE</t>
+          <t>ADJAME_CHATEAU</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>WET327</t>
+          <t>BB_ET524_W</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>GBMBSC14</t>
+          <t>ABRNC01</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ABIDJAN 01</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>2026-05-08 11:33:34</t>
+          <t>2026-05-08 16:07:29</t>
         </is>
       </c>
       <c r="H114" s="3" t="n">
-        <v>46150.48164351852</v>
+        <v>46150.67186342592</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -7168,58 +7724,63 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+          <t>ABO EKPONON CLAUDE</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>06:34:09</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>02:16:35</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AC858</t>
+          <t>IM011</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>DOBA</t>
+          <t>KOBAKRO_ISRAEL</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>WAC858</t>
+          <t>BB_IM011_GW</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>AORNC06</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>SAN-PEDRO</t>
+          <t>ABIDJAN 04</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>2026-05-08 15:08:50</t>
+          <t>2026-05-08 16:30:10</t>
         </is>
       </c>
       <c r="H115" s="3" t="n">
-        <v>46150.63113425926</v>
+        <v>46150.68761574074</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -7228,58 +7789,63 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>OUATTARA MOUMINI</t>
+          <t>COULIBALY ZIE ABOUBAKAR</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>02:58:53</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>01:53:54</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AC865</t>
+          <t>AC634</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LOBOGBA</t>
+          <t>ABINADER</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>WAC865</t>
+          <t>BB_AC634_W</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>BVRNC04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 03</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>2026-05-08 15:17:41</t>
+          <t>2026-05-08 17:02:30</t>
         </is>
       </c>
       <c r="H116" s="3" t="n">
-        <v>46150.63728009259</v>
+        <v>46150.71006944445</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
@@ -7288,58 +7854,63 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>DG</t>
+          <t>NO DG</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>GAUZE GUINANDE DAMIEN</t>
+          <t>DIEFAGA ABDOULAYE</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>02:50:02</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>01:21:34</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AC870</t>
+          <t>ET770</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>MASSADOUGOU</t>
+          <t>GREGUIBRE</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WAC870</t>
+          <t>BB_ET770_W</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>YORNC07</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>2026-05-08 15:41:31</t>
+          <t>2026-05-08 17:24:07</t>
         </is>
       </c>
       <c r="H117" s="3" t="n">
-        <v>46150.65383101852</v>
+        <v>46150.72509259259</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
@@ -7353,53 +7924,58 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>N'CHO ACHY MARC OLIVIER</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>02:26:12</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>00:59:56</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ET620</t>
+          <t>ET368</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GODELILIE</t>
+          <t>BADO17</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>WET620</t>
+          <t>BB_ET368_W</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>YORNC02</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>SAN-PEDRO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>2026-05-08 16:33:13</t>
+          <t>2026-05-08 17:30:54</t>
         </is>
       </c>
       <c r="H118" s="3" t="n">
-        <v>46150.68973379629</v>
+        <v>46150.72979166666</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
@@ -7413,53 +7989,58 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>KONATE BAZOUMANA</t>
+          <t>OUATTARA MOUMINI</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>01:34:30</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>00:53:10</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>IM289</t>
+          <t>ET543</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>KOLIKO</t>
+          <t>YOP_GESCO_BONIKRO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>WIM289</t>
+          <t>BB_ET543_W</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>SIRNC05</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>MAN</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>2026-05-08 16:40:20</t>
+          <t>2026-05-08 17:39:50</t>
         </is>
       </c>
       <c r="H119" s="3" t="n">
-        <v>46150.69467592592</v>
+        <v>46150.73599537037</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
@@ -7473,53 +8054,58 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>YEO DOSONGUY ABRAHAM</t>
+          <t>GNAORE DIDI ERIC</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>01:27:23</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>00:44:14</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>AC421</t>
+          <t>AC673</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>YAM_BARRAGE</t>
+          <t>GESCO_HEVEA</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>WAC421</t>
+          <t>WAC673</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>SIRNC05</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>2026-05-08 16:50:46</t>
+          <t>2026-05-08 17:39:51</t>
         </is>
       </c>
       <c r="H120" s="3" t="n">
-        <v>46150.7019212963</v>
+        <v>46150.73600694445</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -7528,58 +8114,63 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>01:16:57</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>00:44:13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ET473</t>
+          <t>AC671</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FONDI</t>
+          <t>YATSEKOI</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>WET473</t>
+          <t>BB_AC671_W</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>SIRNC05</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>YAMOUSSOUKRO</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>2026-05-08 16:50:51</t>
+          <t>2026-05-08 17:39:51</t>
         </is>
       </c>
       <c r="H121" s="3" t="n">
-        <v>46150.70197916667</v>
+        <v>46150.73600694445</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -7588,58 +8179,63 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>LALLIER DIDIER</t>
+          <t>EKI AKA ADJIRI MARC</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>01:16:52</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>00:44:13</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ET594</t>
+          <t>AC314</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>NIAKARA_CHATEAU</t>
+          <t>GESCO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>WET594</t>
+          <t>WAC314</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>KOMBSC16</t>
+          <t>SIRNC05</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BOUAKE</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NODEB OUTAGE HUA</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>2026-05-08 16:53:57</t>
+          <t>2026-05-08 17:42:51</t>
         </is>
       </c>
       <c r="H122" s="3" t="n">
-        <v>46150.70413194445</v>
+        <v>46150.73809027778</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -7648,58 +8244,63 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>NO DG</t>
+          <t>DG</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>KOUAKOU KOFFI JONATHAN</t>
+          <t>NDA AMANY KOUAKOU</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>01:13:46</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>00:41:13</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>IM184</t>
+          <t>AC995</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KPADAGNOA</t>
+          <t>PHRCIE_ACADJOBA</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>WIM184</t>
+          <t>WAC995</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>YAMBSC12</t>
+          <t>SIRNC05</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>GAGNOA</t>
+          <t>ABIDJAN 02</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NodeB Unavailable</t>
+          <t>NODEB OUTAGE ERIC</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>2026-05-08 16:33:14</t>
+          <t>2026-05-08 17:52:13</t>
         </is>
       </c>
       <c r="H123" s="3" t="n">
-        <v>46150.68974537037</v>
+        <v>46150.74459490741</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -7713,72 +8314,1057 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>KONATE BAZOUMANA</t>
+          <t>TOURE HABIB ARMEL</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>01:34:29</t>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>00:31:51</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>ET465</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GOMON3</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BB_ET465_W</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>SIRNC08</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>ABIDJAN 02</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE ERIC</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:54:23</t>
+        </is>
+      </c>
+      <c r="H124" s="3" t="n">
+        <v>46150.74609953703</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>EKI AKA ADJIRI MARC</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>00:29:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>AC535</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SAGO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BB_AC535_W</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>YORNC07</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>SAN-PEDRO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE ERIC</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:58:22</t>
+        </is>
+      </c>
+      <c r="H125" s="3" t="n">
+        <v>46150.74887731481</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>N'CHO ACHY MARC OLIVIER</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>00:25:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ET327</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>PETITE_BAIE</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>WET327</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>GBMBSC14</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ABIDJAN 01</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-05-08 11:33:34</t>
+        </is>
+      </c>
+      <c r="H126" s="3" t="n">
+        <v>46150.48164351852</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>ABOA KEKRE GUILLAUME BERTRAND</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>06:50:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AC865</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>LOBOGBA</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>WAC865</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-05-08 15:17:41</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="n">
+        <v>46150.63728009259</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>GAUZE GUINANDE DAMIEN</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>03:06:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ET620</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GODELILIE</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>WET620</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:33:13</t>
+        </is>
+      </c>
+      <c r="H128" s="3" t="n">
+        <v>46150.68973379629</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>KONATE BAZOUMANA</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>01:50:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ET594</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>NIAKARA_CHATEAU</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>WET594</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>KOMBSC16</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>BOUAKE</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:53:57</t>
+        </is>
+      </c>
+      <c r="H129" s="3" t="n">
+        <v>46150.70413194445</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>KOUAKOU KOFFI JONATHAN</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>01:30:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>AC701</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>OUANADIEKAHA</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>WAC701</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>BKMBSC15</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>BOUAKE</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:12:10</t>
+        </is>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>46150.71678240741</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>KOUAKOU KOFFI JONATHAN</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>01:11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>IM167</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>KANANGONON</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>WIM167</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>BKMBSC15</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>BOUAKE</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:12:10</t>
+        </is>
+      </c>
+      <c r="H131" s="3" t="n">
+        <v>46150.71678240741</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>KOUAKOU KOFFI JONATHAN</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>01:11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ET781</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>DARAKOKAHA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>WET781</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>BKMBSC15</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>BOUAKE</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:12:10</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="n">
+        <v>46150.71678240741</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>KOUAKOU KOFFI JONATHAN</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>01:11:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ET852</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>TRAWAININKRO</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>WET852</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:19:58</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>46150.72219907407</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>GAUZE GUINANDE DAMIEN</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>01:04:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>IM289</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>KOLIKO</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>WIM289</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>KOMBSC16</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:46:29</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="n">
+        <v>46150.74061342593</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>YEO DOSONGUY ABRAHAM</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>00:37:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ET613</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>LUEHOUAN</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>WET613</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>DALOA</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:52:26</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="n">
+        <v>46150.74474537037</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>DG</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>ASSIE N'GUESSAN FRANCOIS</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>00:31:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ET125</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>KOREGUHE</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>WET125</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>DAMBSC13</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>NODEB OUTAGE HUA</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:52:44</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="n">
+        <v>46150.7449537037</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>GAUZE GUINANDE DAMIEN</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>00:31:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>IM184</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>KPADAGNOA</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>WIM184</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>YAMBSC12</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>GAGNOA</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>NodeB Unavailable</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-05-08 16:33:14</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="n">
+        <v>46150.68974537037</v>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>KONATE BAZOUMANA</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>01:50:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
           <t>IM429</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B138" t="inlineStr">
         <is>
           <t>GADAGO_RURAL</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>WIM429</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D138" t="inlineStr">
         <is>
           <t>YAMBSC12</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E138" t="inlineStr">
         <is>
           <t>GAGNOA</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F138" t="inlineStr">
         <is>
           <t>NodeB Unavailable</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2026-05-08 16:56:43</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="n">
-        <v>46150.70605324074</v>
-      </c>
-      <c r="I124" t="inlineStr">
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:42:48</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="n">
+        <v>46150.73805555556</v>
+      </c>
+      <c r="I138" t="inlineStr">
         <is>
           <t>3G</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>NO DG</t>
-        </is>
-      </c>
-      <c r="K124" t="inlineStr">
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>GAUZE GUINANDE DAMIEN</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>01:11:00</t>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>00:41:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>IM289</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>KOLIKO</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>WIM289</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>KOMBSC16</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MAN</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>NodeB Unavailable</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-05-08 17:58:18</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="n">
+        <v>46150.74881944444</v>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>3G</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>NO DG</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>YEO DOSONGUY ABRAHAM</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-05-08 18:15:39</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>00:25:46</t>
         </is>
       </c>
     </row>
